--- a/预置按键功能介绍.xlsx
+++ b/预置按键功能介绍.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19500" windowHeight="10575" activeTab="1"/>
+    <workbookView windowHeight="18380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -123,10 +123,10 @@
     <t>抽壳</t>
   </si>
   <si>
+    <t>圆弧</t>
+  </si>
+  <si>
     <t>圆</t>
-  </si>
-  <si>
-    <t>圆弧</t>
   </si>
   <si>
     <t>椭圆</t>
@@ -557,9 +557,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -567,13 +566,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -588,22 +580,23 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -617,14 +610,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -632,7 +641,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -640,6 +664,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -654,24 +686,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -685,22 +701,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="5"/>
       <name val="DFPHeiW9-GB"/>
@@ -782,175 +782,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1072,15 +1072,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1092,6 +1083,35 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1135,26 +1155,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1177,10 +1177,10 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1189,137 +1189,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1346,9 +1346,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1861,931 +1858,931 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:Y54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="87.375" customWidth="1"/>
-    <col min="2" max="2" width="1.5" style="35" customWidth="1"/>
-    <col min="3" max="3" width="1.63333333333333" style="35" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="36" customWidth="1"/>
-    <col min="5" max="5" width="1.63333333333333" style="35" customWidth="1"/>
-    <col min="6" max="6" width="15.25" style="36" customWidth="1"/>
-    <col min="7" max="7" width="1.63333333333333" style="35" customWidth="1"/>
-    <col min="8" max="8" width="15.25" style="36" customWidth="1"/>
-    <col min="9" max="9" width="1.625" style="35" customWidth="1"/>
-    <col min="10" max="10" width="2.05833333333333" style="35" customWidth="1"/>
-    <col min="11" max="11" width="1.625" customWidth="1"/>
-    <col min="12" max="12" width="15.25" customWidth="1"/>
-    <col min="13" max="13" width="1.625" customWidth="1"/>
-    <col min="14" max="14" width="15.25" customWidth="1"/>
-    <col min="15" max="15" width="1.625" customWidth="1"/>
-    <col min="16" max="16" width="15.25" customWidth="1"/>
-    <col min="17" max="17" width="1.625" customWidth="1"/>
-    <col min="18" max="18" width="2.25" customWidth="1"/>
-    <col min="19" max="19" width="1.53333333333333" customWidth="1"/>
-    <col min="21" max="21" width="1.53333333333333" customWidth="1"/>
-    <col min="23" max="23" width="1.53333333333333" customWidth="1"/>
-    <col min="25" max="25" width="1.53333333333333" customWidth="1"/>
+    <col min="1" max="1" width="87.3727272727273" customWidth="1"/>
+    <col min="2" max="2" width="1.5" style="34" customWidth="1"/>
+    <col min="3" max="3" width="1.63636363636364" style="34" customWidth="1"/>
+    <col min="4" max="4" width="15.2545454545455" style="35" customWidth="1"/>
+    <col min="5" max="5" width="1.63636363636364" style="34" customWidth="1"/>
+    <col min="6" max="6" width="15.2545454545455" style="35" customWidth="1"/>
+    <col min="7" max="7" width="1.63636363636364" style="34" customWidth="1"/>
+    <col min="8" max="8" width="15.2545454545455" style="35" customWidth="1"/>
+    <col min="9" max="9" width="1.62727272727273" style="34" customWidth="1"/>
+    <col min="10" max="10" width="2.05454545454545" style="34" customWidth="1"/>
+    <col min="11" max="11" width="1.62727272727273" customWidth="1"/>
+    <col min="12" max="12" width="15.2545454545455" customWidth="1"/>
+    <col min="13" max="13" width="1.62727272727273" customWidth="1"/>
+    <col min="14" max="14" width="15.2545454545455" customWidth="1"/>
+    <col min="15" max="15" width="1.62727272727273" customWidth="1"/>
+    <col min="16" max="16" width="15.2545454545455" customWidth="1"/>
+    <col min="17" max="17" width="1.62727272727273" customWidth="1"/>
+    <col min="18" max="18" width="2.25454545454545" customWidth="1"/>
+    <col min="19" max="19" width="1.53636363636364" customWidth="1"/>
+    <col min="21" max="21" width="1.53636363636364" customWidth="1"/>
+    <col min="23" max="23" width="1.53636363636364" customWidth="1"/>
+    <col min="25" max="25" width="1.53636363636364" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="11" customHeight="1"/>
     <row r="2" ht="24" customHeight="1" spans="3:25">
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="39"/>
-      <c r="K2" s="54" t="s">
+      <c r="D2" s="37"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="38"/>
+      <c r="K2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="38"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="39"/>
-      <c r="S2" s="54" t="s">
+      <c r="L2" s="37"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="38"/>
+      <c r="S2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="38"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="39"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="38"/>
     </row>
     <row r="3" ht="11" customHeight="1" spans="3:25">
-      <c r="C3" s="40"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="55"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="55"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="61"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="61"/>
-      <c r="X3" s="60"/>
-      <c r="Y3" s="69"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="54"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="41"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="54"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="60"/>
+      <c r="V3" s="59"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="59"/>
+      <c r="Y3" s="68"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="3:25">
-      <c r="C4" s="43"/>
-      <c r="D4" s="44" t="s">
+      <c r="C4" s="42"/>
+      <c r="D4" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="44" t="s">
+      <c r="E4" s="44"/>
+      <c r="F4" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="45"/>
-      <c r="H4" s="44" t="s">
+      <c r="G4" s="44"/>
+      <c r="H4" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="56"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="56"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="63">
+      <c r="I4" s="55"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="55"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="62">
         <v>7</v>
       </c>
-      <c r="U4" s="64"/>
-      <c r="V4" s="63">
+      <c r="U4" s="63"/>
+      <c r="V4" s="62">
         <v>8</v>
       </c>
-      <c r="W4" s="64"/>
-      <c r="X4" s="63">
+      <c r="W4" s="63"/>
+      <c r="X4" s="62">
         <v>9</v>
       </c>
-      <c r="Y4" s="70"/>
+      <c r="Y4" s="69"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="3:25">
-      <c r="C5" s="46"/>
-      <c r="D5" s="47" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="47" t="s">
+      <c r="E5" s="47"/>
+      <c r="F5" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="48"/>
-      <c r="H5" s="47" t="s">
+      <c r="G5" s="47"/>
+      <c r="H5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="57"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="57"/>
-      <c r="S5" s="62"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="64"/>
-      <c r="V5" s="63"/>
-      <c r="W5" s="64"/>
-      <c r="X5" s="63"/>
-      <c r="Y5" s="70"/>
+      <c r="I5" s="56"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="56"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="62"/>
+      <c r="U5" s="63"/>
+      <c r="V5" s="62"/>
+      <c r="W5" s="63"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="69"/>
     </row>
     <row r="6" ht="11" customHeight="1" spans="3:25">
-      <c r="C6" s="46"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="57"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="57"/>
-      <c r="S6" s="62"/>
-      <c r="T6" s="65"/>
-      <c r="U6" s="64"/>
-      <c r="V6" s="65"/>
-      <c r="W6" s="64"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="70"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="56"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="56"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="64"/>
+      <c r="U6" s="63"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="63"/>
+      <c r="X6" s="64"/>
+      <c r="Y6" s="69"/>
     </row>
     <row r="7" ht="11" customHeight="1" spans="3:25">
-      <c r="C7" s="43"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="56"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="56"/>
-      <c r="S7" s="62"/>
-      <c r="T7" s="65"/>
-      <c r="U7" s="64"/>
-      <c r="V7" s="65"/>
-      <c r="W7" s="64"/>
-      <c r="X7" s="65"/>
-      <c r="Y7" s="70"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="55"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="55"/>
+      <c r="S7" s="61"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="63"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="63"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="69"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="3:25">
-      <c r="C8" s="43"/>
-      <c r="D8" s="44" t="s">
+      <c r="C8" s="42"/>
+      <c r="D8" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="44" t="s">
+      <c r="E8" s="44"/>
+      <c r="F8" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="45"/>
-      <c r="H8" s="44" t="s">
+      <c r="G8" s="44"/>
+      <c r="H8" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="56"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="56"/>
-      <c r="S8" s="62"/>
-      <c r="T8" s="63">
+      <c r="I8" s="55"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="55"/>
+      <c r="S8" s="61"/>
+      <c r="T8" s="62">
         <v>4</v>
       </c>
-      <c r="U8" s="64"/>
-      <c r="V8" s="63">
+      <c r="U8" s="63"/>
+      <c r="V8" s="62">
         <v>5</v>
       </c>
-      <c r="W8" s="64"/>
-      <c r="X8" s="63">
+      <c r="W8" s="63"/>
+      <c r="X8" s="62">
         <v>6</v>
       </c>
-      <c r="Y8" s="70"/>
+      <c r="Y8" s="69"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="3:25">
-      <c r="C9" s="46"/>
-      <c r="D9" s="47" t="s">
+      <c r="C9" s="45"/>
+      <c r="D9" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="47" t="s">
+      <c r="E9" s="47"/>
+      <c r="F9" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="48"/>
-      <c r="H9" s="47" t="s">
+      <c r="G9" s="47"/>
+      <c r="H9" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="57"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="48"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="57"/>
-      <c r="S9" s="62"/>
-      <c r="T9" s="63"/>
-      <c r="U9" s="64"/>
-      <c r="V9" s="63"/>
-      <c r="W9" s="64"/>
-      <c r="X9" s="63"/>
-      <c r="Y9" s="70"/>
+      <c r="I9" s="56"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="56"/>
+      <c r="S9" s="61"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="63"/>
+      <c r="V9" s="62"/>
+      <c r="W9" s="63"/>
+      <c r="X9" s="62"/>
+      <c r="Y9" s="69"/>
     </row>
     <row r="10" ht="11" customHeight="1" spans="3:25">
-      <c r="C10" s="46"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="57"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="49"/>
-      <c r="O10" s="48"/>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="57"/>
-      <c r="S10" s="62"/>
-      <c r="T10" s="65"/>
-      <c r="U10" s="64"/>
-      <c r="V10" s="65"/>
-      <c r="W10" s="64"/>
-      <c r="X10" s="65"/>
-      <c r="Y10" s="70"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="56"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="56"/>
+      <c r="S10" s="61"/>
+      <c r="T10" s="64"/>
+      <c r="U10" s="63"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="63"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="69"/>
     </row>
     <row r="11" ht="11" customHeight="1" spans="3:25">
-      <c r="C11" s="43"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="56"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="45"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="50"/>
-      <c r="Q11" s="56"/>
-      <c r="S11" s="62"/>
-      <c r="T11" s="65"/>
-      <c r="U11" s="64"/>
-      <c r="V11" s="65"/>
-      <c r="W11" s="64"/>
-      <c r="X11" s="65"/>
-      <c r="Y11" s="70"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="55"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="55"/>
+      <c r="S11" s="61"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="63"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="63"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="69"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="3:25">
-      <c r="C12" s="43"/>
-      <c r="D12" s="44" t="s">
+      <c r="C12" s="42"/>
+      <c r="D12" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="45"/>
-      <c r="F12" s="44" t="s">
+      <c r="E12" s="44"/>
+      <c r="F12" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="45"/>
-      <c r="H12" s="44" t="s">
+      <c r="G12" s="44"/>
+      <c r="H12" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="56"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="56"/>
-      <c r="S12" s="62"/>
-      <c r="T12" s="63">
+      <c r="I12" s="55"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="55"/>
+      <c r="S12" s="61"/>
+      <c r="T12" s="62">
         <v>1</v>
       </c>
-      <c r="U12" s="64"/>
-      <c r="V12" s="63">
+      <c r="U12" s="63"/>
+      <c r="V12" s="62">
         <v>2</v>
       </c>
-      <c r="W12" s="64"/>
-      <c r="X12" s="63">
+      <c r="W12" s="63"/>
+      <c r="X12" s="62">
         <v>3</v>
       </c>
-      <c r="Y12" s="70"/>
+      <c r="Y12" s="69"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="3:25">
-      <c r="C13" s="46"/>
-      <c r="D13" s="47" t="s">
+      <c r="C13" s="45"/>
+      <c r="D13" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="48"/>
-      <c r="F13" s="47" t="s">
+      <c r="E13" s="47"/>
+      <c r="F13" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="48"/>
-      <c r="H13" s="47" t="s">
+      <c r="G13" s="47"/>
+      <c r="H13" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="57"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="48"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="57"/>
-      <c r="S13" s="62"/>
-      <c r="T13" s="63"/>
-      <c r="U13" s="64"/>
-      <c r="V13" s="63"/>
-      <c r="W13" s="64"/>
-      <c r="X13" s="63"/>
-      <c r="Y13" s="70"/>
+      <c r="I13" s="56"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="56"/>
+      <c r="S13" s="61"/>
+      <c r="T13" s="62"/>
+      <c r="U13" s="63"/>
+      <c r="V13" s="62"/>
+      <c r="W13" s="63"/>
+      <c r="X13" s="62"/>
+      <c r="Y13" s="69"/>
     </row>
     <row r="14" ht="11" customHeight="1" spans="3:25">
-      <c r="C14" s="46"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="57"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="48"/>
-      <c r="N14" s="49"/>
-      <c r="O14" s="48"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="57"/>
-      <c r="S14" s="62"/>
-      <c r="T14" s="65"/>
-      <c r="U14" s="64"/>
-      <c r="V14" s="65"/>
-      <c r="W14" s="64"/>
-      <c r="X14" s="65"/>
-      <c r="Y14" s="70"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="56"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="56"/>
+      <c r="S14" s="61"/>
+      <c r="T14" s="64"/>
+      <c r="U14" s="63"/>
+      <c r="V14" s="64"/>
+      <c r="W14" s="63"/>
+      <c r="X14" s="64"/>
+      <c r="Y14" s="69"/>
     </row>
     <row r="15" ht="11" customHeight="1" spans="3:25">
-      <c r="C15" s="43"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="56"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="56"/>
-      <c r="S15" s="62"/>
-      <c r="T15" s="65"/>
-      <c r="U15" s="64"/>
-      <c r="V15" s="65"/>
-      <c r="W15" s="64"/>
-      <c r="X15" s="65"/>
-      <c r="Y15" s="70"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="55"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="55"/>
+      <c r="S15" s="61"/>
+      <c r="T15" s="64"/>
+      <c r="U15" s="63"/>
+      <c r="V15" s="64"/>
+      <c r="W15" s="63"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="69"/>
     </row>
     <row r="16" ht="24" customHeight="1" spans="3:25">
-      <c r="C16" s="43"/>
-      <c r="D16" s="44" t="s">
+      <c r="C16" s="42"/>
+      <c r="D16" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="44" t="s">
+      <c r="E16" s="44"/>
+      <c r="F16" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="45"/>
-      <c r="H16" s="44" t="s">
+      <c r="G16" s="44"/>
+      <c r="H16" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="56"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="45"/>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="56"/>
-      <c r="S16" s="62"/>
-      <c r="T16" s="63">
+      <c r="I16" s="55"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="55"/>
+      <c r="S16" s="61"/>
+      <c r="T16" s="62">
         <v>0</v>
       </c>
-      <c r="U16" s="64"/>
-      <c r="V16" s="63" t="s">
+      <c r="U16" s="63"/>
+      <c r="V16" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="W16" s="64"/>
-      <c r="X16" s="63" t="s">
+      <c r="W16" s="63"/>
+      <c r="X16" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="Y16" s="70"/>
+      <c r="Y16" s="69"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="3:25">
-      <c r="C17" s="46"/>
-      <c r="D17" s="47" t="s">
+      <c r="C17" s="45"/>
+      <c r="D17" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="48"/>
-      <c r="F17" s="47" t="s">
+      <c r="E17" s="47"/>
+      <c r="F17" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="48"/>
-      <c r="H17" s="47" t="s">
+      <c r="G17" s="47"/>
+      <c r="H17" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="57"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="47"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="47"/>
-      <c r="O17" s="48"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="57"/>
-      <c r="S17" s="62"/>
-      <c r="T17" s="63"/>
-      <c r="U17" s="64"/>
-      <c r="V17" s="63"/>
-      <c r="W17" s="64"/>
-      <c r="X17" s="63"/>
-      <c r="Y17" s="70"/>
+      <c r="I17" s="56"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="47"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="56"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="62"/>
+      <c r="U17" s="63"/>
+      <c r="V17" s="62"/>
+      <c r="W17" s="63"/>
+      <c r="X17" s="62"/>
+      <c r="Y17" s="69"/>
     </row>
     <row r="18" ht="11" customHeight="1" spans="3:25">
-      <c r="C18" s="51"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="58"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="52"/>
-      <c r="Q18" s="58"/>
-      <c r="S18" s="66"/>
-      <c r="T18" s="67"/>
-      <c r="U18" s="68"/>
-      <c r="V18" s="67"/>
-      <c r="W18" s="68"/>
-      <c r="X18" s="67"/>
-      <c r="Y18" s="71"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="57"/>
+      <c r="K18" s="50"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="52"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="57"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="66"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="66"/>
+      <c r="W18" s="67"/>
+      <c r="X18" s="66"/>
+      <c r="Y18" s="70"/>
     </row>
     <row r="19" ht="11" customHeight="1" spans="11:17">
-      <c r="K19" s="35"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="35"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="34"/>
     </row>
     <row r="20" ht="24" customHeight="1" spans="3:25">
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="38"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
-      <c r="K20" s="54" t="s">
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="37"/>
+      <c r="I20" s="38"/>
+      <c r="K20" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="38"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="39"/>
-      <c r="S20" s="54" t="s">
+      <c r="L20" s="37"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="38"/>
+      <c r="S20" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="T20" s="38"/>
-      <c r="U20" s="39"/>
-      <c r="V20" s="38"/>
-      <c r="W20" s="39"/>
-      <c r="X20" s="38"/>
-      <c r="Y20" s="39"/>
+      <c r="T20" s="37"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="37"/>
+      <c r="W20" s="38"/>
+      <c r="X20" s="37"/>
+      <c r="Y20" s="38"/>
     </row>
     <row r="21" ht="11" customHeight="1" spans="3:25">
-      <c r="C21" s="40"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="55"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="55"/>
-      <c r="S21" s="59"/>
-      <c r="T21" s="60"/>
-      <c r="U21" s="61"/>
-      <c r="V21" s="60"/>
-      <c r="W21" s="61"/>
-      <c r="X21" s="60"/>
-      <c r="Y21" s="69"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="54"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="54"/>
+      <c r="S21" s="58"/>
+      <c r="T21" s="59"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="59"/>
+      <c r="W21" s="60"/>
+      <c r="X21" s="59"/>
+      <c r="Y21" s="68"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="3:25">
-      <c r="C22" s="43"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="56"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="56"/>
-      <c r="S22" s="62"/>
-      <c r="T22" s="63" t="s">
+      <c r="C22" s="42"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="55"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="55"/>
+      <c r="S22" s="61"/>
+      <c r="T22" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="U22" s="64"/>
-      <c r="V22" s="63" t="s">
+      <c r="U22" s="63"/>
+      <c r="V22" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="W22" s="64"/>
-      <c r="X22" s="63" t="s">
+      <c r="W22" s="63"/>
+      <c r="X22" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="Y22" s="70"/>
+      <c r="Y22" s="69"/>
     </row>
     <row r="23" ht="24" customHeight="1" spans="3:25">
-      <c r="C23" s="46"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="57"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="48"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="57"/>
-      <c r="S23" s="62"/>
-      <c r="T23" s="63"/>
-      <c r="U23" s="64"/>
-      <c r="V23" s="63"/>
-      <c r="W23" s="64"/>
-      <c r="X23" s="63"/>
-      <c r="Y23" s="70"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="56"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="47"/>
+      <c r="N23" s="46"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="46"/>
+      <c r="Q23" s="56"/>
+      <c r="S23" s="61"/>
+      <c r="T23" s="62"/>
+      <c r="U23" s="63"/>
+      <c r="V23" s="62"/>
+      <c r="W23" s="63"/>
+      <c r="X23" s="62"/>
+      <c r="Y23" s="69"/>
     </row>
     <row r="24" ht="11" customHeight="1" spans="3:25">
-      <c r="C24" s="46"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="57"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="49"/>
-      <c r="O24" s="48"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="57"/>
-      <c r="S24" s="62"/>
-      <c r="T24" s="65"/>
-      <c r="U24" s="64"/>
-      <c r="V24" s="65"/>
-      <c r="W24" s="64"/>
-      <c r="X24" s="65"/>
-      <c r="Y24" s="70"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="56"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="56"/>
+      <c r="S24" s="61"/>
+      <c r="T24" s="64"/>
+      <c r="U24" s="63"/>
+      <c r="V24" s="64"/>
+      <c r="W24" s="63"/>
+      <c r="X24" s="64"/>
+      <c r="Y24" s="69"/>
     </row>
     <row r="25" ht="11" customHeight="1" spans="3:25">
-      <c r="C25" s="43"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="56"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="45"/>
-      <c r="P25" s="50"/>
-      <c r="Q25" s="56"/>
-      <c r="S25" s="62"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="64"/>
-      <c r="V25" s="65"/>
-      <c r="W25" s="64"/>
-      <c r="X25" s="65"/>
-      <c r="Y25" s="70"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="55"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="44"/>
+      <c r="P25" s="49"/>
+      <c r="Q25" s="55"/>
+      <c r="S25" s="61"/>
+      <c r="T25" s="64"/>
+      <c r="U25" s="63"/>
+      <c r="V25" s="64"/>
+      <c r="W25" s="63"/>
+      <c r="X25" s="64"/>
+      <c r="Y25" s="69"/>
     </row>
     <row r="26" ht="24" customHeight="1" spans="3:25">
-      <c r="C26" s="43"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="56"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="45"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="56"/>
-      <c r="S26" s="62"/>
-      <c r="T26" s="63" t="s">
+      <c r="C26" s="42"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="55"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="55"/>
+      <c r="S26" s="61"/>
+      <c r="T26" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="U26" s="64"/>
-      <c r="V26" s="63" t="s">
+      <c r="U26" s="63"/>
+      <c r="V26" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="W26" s="64"/>
-      <c r="X26" s="63" t="s">
+      <c r="W26" s="63"/>
+      <c r="X26" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="Y26" s="70"/>
+      <c r="Y26" s="69"/>
     </row>
     <row r="27" ht="24" customHeight="1" spans="3:25">
-      <c r="C27" s="46"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="57"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="57"/>
-      <c r="S27" s="62"/>
-      <c r="T27" s="63"/>
-      <c r="U27" s="64"/>
-      <c r="V27" s="63"/>
-      <c r="W27" s="64"/>
-      <c r="X27" s="63"/>
-      <c r="Y27" s="70"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="56"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="47"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="56"/>
+      <c r="S27" s="61"/>
+      <c r="T27" s="62"/>
+      <c r="U27" s="63"/>
+      <c r="V27" s="62"/>
+      <c r="W27" s="63"/>
+      <c r="X27" s="62"/>
+      <c r="Y27" s="69"/>
     </row>
     <row r="28" ht="11" customHeight="1" spans="3:25">
-      <c r="C28" s="46"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="57"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="49"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="57"/>
-      <c r="S28" s="62"/>
-      <c r="T28" s="65"/>
-      <c r="U28" s="64"/>
-      <c r="V28" s="65"/>
-      <c r="W28" s="64"/>
-      <c r="X28" s="65"/>
-      <c r="Y28" s="70"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="56"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="47"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="47"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="56"/>
+      <c r="S28" s="61"/>
+      <c r="T28" s="64"/>
+      <c r="U28" s="63"/>
+      <c r="V28" s="64"/>
+      <c r="W28" s="63"/>
+      <c r="X28" s="64"/>
+      <c r="Y28" s="69"/>
     </row>
     <row r="29" ht="11" customHeight="1" spans="3:25">
-      <c r="C29" s="43"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="56"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="56"/>
-      <c r="S29" s="62"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="64"/>
-      <c r="V29" s="65"/>
-      <c r="W29" s="64"/>
-      <c r="X29" s="65"/>
-      <c r="Y29" s="70"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="55"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="49"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="49"/>
+      <c r="O29" s="44"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="55"/>
+      <c r="S29" s="61"/>
+      <c r="T29" s="64"/>
+      <c r="U29" s="63"/>
+      <c r="V29" s="64"/>
+      <c r="W29" s="63"/>
+      <c r="X29" s="64"/>
+      <c r="Y29" s="69"/>
     </row>
     <row r="30" ht="24" customHeight="1" spans="3:25">
-      <c r="C30" s="43"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="56"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="56"/>
-      <c r="S30" s="62"/>
-      <c r="T30" s="63" t="s">
+      <c r="C30" s="42"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="55"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="44"/>
+      <c r="P30" s="43"/>
+      <c r="Q30" s="55"/>
+      <c r="S30" s="61"/>
+      <c r="T30" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="U30" s="64"/>
-      <c r="V30" s="63" t="s">
+      <c r="U30" s="63"/>
+      <c r="V30" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="W30" s="64"/>
-      <c r="X30" s="63" t="s">
+      <c r="W30" s="63"/>
+      <c r="X30" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="Y30" s="70"/>
+      <c r="Y30" s="69"/>
     </row>
     <row r="31" ht="24" customHeight="1" spans="3:25">
-      <c r="C31" s="46"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="57"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="47"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="47"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="57"/>
-      <c r="S31" s="62"/>
-      <c r="T31" s="63"/>
-      <c r="U31" s="64"/>
-      <c r="V31" s="63"/>
-      <c r="W31" s="64"/>
-      <c r="X31" s="63"/>
-      <c r="Y31" s="70"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="56"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="47"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="47"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="56"/>
+      <c r="S31" s="61"/>
+      <c r="T31" s="62"/>
+      <c r="U31" s="63"/>
+      <c r="V31" s="62"/>
+      <c r="W31" s="63"/>
+      <c r="X31" s="62"/>
+      <c r="Y31" s="69"/>
     </row>
     <row r="32" ht="11" customHeight="1" spans="3:25">
-      <c r="C32" s="46"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="57"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="48"/>
-      <c r="N32" s="49"/>
-      <c r="O32" s="48"/>
-      <c r="P32" s="49"/>
-      <c r="Q32" s="57"/>
-      <c r="S32" s="62"/>
-      <c r="T32" s="65"/>
-      <c r="U32" s="64"/>
-      <c r="V32" s="65"/>
-      <c r="W32" s="64"/>
-      <c r="X32" s="65"/>
-      <c r="Y32" s="70"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="48"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="56"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="48"/>
+      <c r="M32" s="47"/>
+      <c r="N32" s="48"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="56"/>
+      <c r="S32" s="61"/>
+      <c r="T32" s="64"/>
+      <c r="U32" s="63"/>
+      <c r="V32" s="64"/>
+      <c r="W32" s="63"/>
+      <c r="X32" s="64"/>
+      <c r="Y32" s="69"/>
     </row>
     <row r="33" ht="11" customHeight="1" spans="3:25">
-      <c r="C33" s="43"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="56"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="50"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="45"/>
-      <c r="P33" s="50"/>
-      <c r="Q33" s="56"/>
-      <c r="S33" s="62"/>
-      <c r="T33" s="65"/>
-      <c r="U33" s="64"/>
-      <c r="V33" s="65"/>
-      <c r="W33" s="64"/>
-      <c r="X33" s="65"/>
-      <c r="Y33" s="70"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="55"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="49"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="44"/>
+      <c r="P33" s="49"/>
+      <c r="Q33" s="55"/>
+      <c r="S33" s="61"/>
+      <c r="T33" s="64"/>
+      <c r="U33" s="63"/>
+      <c r="V33" s="64"/>
+      <c r="W33" s="63"/>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="69"/>
     </row>
     <row r="34" ht="24" customHeight="1" spans="3:25">
-      <c r="C34" s="43"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="56"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="44"/>
-      <c r="M34" s="45"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="45"/>
-      <c r="P34" s="44"/>
-      <c r="Q34" s="56"/>
-      <c r="S34" s="62"/>
-      <c r="T34" s="63" t="s">
+      <c r="C34" s="42"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="55"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="43"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="43"/>
+      <c r="O34" s="44"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="55"/>
+      <c r="S34" s="61"/>
+      <c r="T34" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="U34" s="64"/>
-      <c r="V34" s="63" t="s">
+      <c r="U34" s="63"/>
+      <c r="V34" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="W34" s="64"/>
-      <c r="X34" s="63" t="s">
+      <c r="W34" s="63"/>
+      <c r="X34" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="Y34" s="70"/>
+      <c r="Y34" s="69"/>
     </row>
     <row r="35" ht="24" customHeight="1" spans="3:25">
-      <c r="C35" s="46"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="57"/>
-      <c r="K35" s="46"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="48"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="57"/>
-      <c r="S35" s="62"/>
-      <c r="T35" s="63"/>
-      <c r="U35" s="64"/>
-      <c r="V35" s="63"/>
-      <c r="W35" s="64"/>
-      <c r="X35" s="63"/>
-      <c r="Y35" s="70"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="56"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="47"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="46"/>
+      <c r="Q35" s="56"/>
+      <c r="S35" s="61"/>
+      <c r="T35" s="62"/>
+      <c r="U35" s="63"/>
+      <c r="V35" s="62"/>
+      <c r="W35" s="63"/>
+      <c r="X35" s="62"/>
+      <c r="Y35" s="69"/>
     </row>
     <row r="36" ht="11" customHeight="1" spans="3:25">
-      <c r="C36" s="51"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="58"/>
-      <c r="K36" s="51"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="53"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="53"/>
-      <c r="P36" s="52"/>
-      <c r="Q36" s="58"/>
-      <c r="S36" s="66"/>
-      <c r="T36" s="67"/>
-      <c r="U36" s="68"/>
-      <c r="V36" s="67"/>
-      <c r="W36" s="68"/>
-      <c r="X36" s="67"/>
-      <c r="Y36" s="71"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="57"/>
+      <c r="K36" s="50"/>
+      <c r="L36" s="51"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="52"/>
+      <c r="P36" s="51"/>
+      <c r="Q36" s="57"/>
+      <c r="S36" s="65"/>
+      <c r="T36" s="66"/>
+      <c r="U36" s="67"/>
+      <c r="V36" s="66"/>
+      <c r="W36" s="67"/>
+      <c r="X36" s="66"/>
+      <c r="Y36" s="70"/>
     </row>
     <row r="37" ht="11" customHeight="1"/>
     <row r="38" ht="24" customHeight="1"/>
@@ -2847,53 +2844,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B2:P18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="3.15833333333333" style="8" customWidth="1"/>
+    <col min="1" max="1" width="3.15454545454545" style="8" customWidth="1"/>
     <col min="2" max="2" width="2.5" style="8" customWidth="1"/>
-    <col min="3" max="3" width="8.875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="1.425" style="8" customWidth="1"/>
-    <col min="5" max="6" width="8.875" style="8" customWidth="1"/>
-    <col min="7" max="7" width="1.425" style="8" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="8.87272727272727" style="8" customWidth="1"/>
+    <col min="4" max="4" width="1.42727272727273" style="8" customWidth="1"/>
+    <col min="5" max="6" width="8.87272727272727" style="8" customWidth="1"/>
+    <col min="7" max="7" width="1.42727272727273" style="8" customWidth="1"/>
+    <col min="8" max="8" width="8.87272727272727" style="8" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="8" customWidth="1"/>
     <col min="10" max="10" width="2.5" style="8" customWidth="1"/>
-    <col min="11" max="11" width="12.875" style="8" customWidth="1"/>
-    <col min="12" max="12" width="1.425" style="8" customWidth="1"/>
-    <col min="13" max="14" width="8.875" style="29" customWidth="1"/>
-    <col min="15" max="15" width="1.425" style="29" customWidth="1"/>
-    <col min="16" max="16" width="12.875" customWidth="1"/>
+    <col min="11" max="11" width="12.8727272727273" style="8" customWidth="1"/>
+    <col min="12" max="12" width="1.42727272727273" style="8" customWidth="1"/>
+    <col min="13" max="14" width="8.87272727272727" style="28" customWidth="1"/>
+    <col min="15" max="15" width="1.42727272727273" style="28" customWidth="1"/>
+    <col min="16" max="16" width="12.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" ht="16" customHeight="1" spans="2:16">
       <c r="B2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="30" t="s">
+      <c r="D2" s="30"/>
+      <c r="E2" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="30" t="s">
+      <c r="F2" s="29"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="29" t="s">
         <v>45</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="31"/>
-      <c r="M2" s="30" t="s">
+      <c r="L2" s="30"/>
+      <c r="M2" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="N2" s="30"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="30" t="s">
+      <c r="N2" s="29"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="29" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2902,70 +2899,70 @@
       <c r="C3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="31"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="31" t="s">
         <v>49</v>
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="5"/>
-      <c r="L3" s="31"/>
+      <c r="L3" s="30"/>
       <c r="M3" s="5" t="s">
         <v>50</v>
       </c>
       <c r="N3" s="5"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="32"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="31"/>
     </row>
     <row r="4" ht="7" customHeight="1" spans="2:16">
       <c r="B4" s="7"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
       <c r="J4" s="7"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
     </row>
     <row r="5" ht="16" customHeight="1" spans="2:16">
       <c r="B5" s="7"/>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="30" t="s">
+      <c r="D5" s="30"/>
+      <c r="E5" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="30" t="s">
+      <c r="G5" s="30"/>
+      <c r="H5" s="29" t="s">
         <v>54</v>
       </c>
       <c r="J5" s="7"/>
-      <c r="K5" s="30" t="s">
+      <c r="K5" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="31"/>
-      <c r="M5" s="30" t="s">
+      <c r="L5" s="30"/>
+      <c r="M5" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="N5" s="30" t="s">
+      <c r="N5" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="O5" s="31"/>
-      <c r="P5" s="30" t="s">
+      <c r="O5" s="30"/>
+      <c r="P5" s="29" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2974,68 +2971,68 @@
       <c r="C6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="31"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="31"/>
+      <c r="G6" s="30"/>
       <c r="H6" s="5" t="s">
         <v>57</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="31"/>
+      <c r="L6" s="30"/>
       <c r="M6" s="5" t="s">
         <v>58</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="O6" s="31"/>
+      <c r="O6" s="30"/>
       <c r="P6" s="5"/>
     </row>
     <row r="7" ht="7" customHeight="1" spans="2:16">
       <c r="B7" s="7"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
       <c r="J7" s="7"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
     </row>
     <row r="8" ht="16" customHeight="1" spans="2:16">
       <c r="B8" s="7"/>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="30" t="s">
+      <c r="D8" s="30"/>
+      <c r="E8" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="30" t="s">
+      <c r="F8" s="29"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="29" t="s">
         <v>62</v>
       </c>
       <c r="J8" s="7"/>
-      <c r="K8" s="30" t="s">
+      <c r="K8" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="L8" s="31"/>
-      <c r="M8" s="30" t="s">
+      <c r="L8" s="30"/>
+      <c r="M8" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="N8" s="30"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="30" t="s">
+      <c r="N8" s="29"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="29" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3070,198 +3067,198 @@
     </row>
     <row r="11" ht="16" customHeight="1" spans="2:16">
       <c r="B11" s="7"/>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="33" t="s">
+      <c r="D11" s="30"/>
+      <c r="E11" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="33"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="33" t="s">
+      <c r="F11" s="32"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="32" t="s">
         <v>45</v>
       </c>
       <c r="J11" s="7"/>
-      <c r="K11" s="33" t="s">
+      <c r="K11" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="L11" s="31"/>
-      <c r="M11" s="33" t="s">
+      <c r="L11" s="30"/>
+      <c r="M11" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="33"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="33" t="s">
+      <c r="N11" s="32"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="32" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" spans="2:16">
       <c r="B12" s="7"/>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="30"/>
+      <c r="E12" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="34" t="s">
+      <c r="F12" s="12"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="33" t="s">
         <v>69</v>
       </c>
       <c r="J12" s="7"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="13" t="s">
+      <c r="K12" s="12"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="N12" s="13"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="34"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="33"/>
     </row>
     <row r="13" ht="7" customHeight="1" spans="2:16">
       <c r="B13" s="7"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
       <c r="J13" s="7"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
     </row>
     <row r="14" ht="16" customHeight="1" spans="2:16">
       <c r="B14" s="7"/>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="33" t="s">
+      <c r="D14" s="30"/>
+      <c r="E14" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="33" t="s">
+      <c r="F14" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="31"/>
-      <c r="H14" s="33" t="s">
+      <c r="G14" s="30"/>
+      <c r="H14" s="32" t="s">
         <v>54</v>
       </c>
       <c r="J14" s="7"/>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="L14" s="31"/>
-      <c r="M14" s="33" t="s">
+      <c r="L14" s="30"/>
+      <c r="M14" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="N14" s="33" t="s">
+      <c r="N14" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="O14" s="31"/>
-      <c r="P14" s="33" t="s">
+      <c r="O14" s="30"/>
+      <c r="P14" s="32" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" spans="2:16">
       <c r="B15" s="7"/>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="13" t="s">
+      <c r="D15" s="30"/>
+      <c r="E15" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="13" t="s">
+      <c r="F15" s="12"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="12" t="s">
         <v>72</v>
       </c>
       <c r="J15" s="7"/>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="L15" s="31"/>
-      <c r="M15" s="13" t="s">
+      <c r="L15" s="30"/>
+      <c r="M15" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="N15" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="O15" s="31"/>
-      <c r="P15" s="13" t="s">
+      <c r="O15" s="30"/>
+      <c r="P15" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="16" ht="7" customHeight="1" spans="2:16">
       <c r="B16" s="7"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
       <c r="J16" s="7"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
     </row>
     <row r="17" ht="16" customHeight="1" spans="2:16">
       <c r="B17" s="7"/>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="33" t="s">
+      <c r="D17" s="30"/>
+      <c r="E17" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="33"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="33" t="s">
+      <c r="F17" s="32"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="32" t="s">
         <v>62</v>
       </c>
       <c r="J17" s="7"/>
-      <c r="K17" s="33" t="s">
+      <c r="K17" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="L17" s="31"/>
-      <c r="M17" s="33" t="s">
+      <c r="L17" s="30"/>
+      <c r="M17" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="N17" s="33"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="33" t="s">
+      <c r="N17" s="32"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="32" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1" spans="2:16">
       <c r="B18" s="7"/>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="13"/>
-      <c r="H18" s="13" t="s">
+      <c r="F18" s="12"/>
+      <c r="H18" s="12" t="s">
         <v>77</v>
       </c>
       <c r="J18" s="7"/>
-      <c r="K18" s="13"/>
-      <c r="M18" s="13" t="s">
+      <c r="K18" s="12"/>
+      <c r="M18" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="N18" s="13"/>
+      <c r="N18" s="12"/>
       <c r="O18" s="8"/>
-      <c r="P18" s="13"/>
+      <c r="P18" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3293,17 +3290,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
-    <col min="2" max="2" width="7.06666666666667" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="2.61666666666667" customWidth="1"/>
-    <col min="5" max="5" width="3.225" customWidth="1"/>
-    <col min="6" max="6" width="8.875" customWidth="1"/>
-    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="7.06363636363636" customWidth="1"/>
+    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
+    <col min="4" max="4" width="2.61818181818182" customWidth="1"/>
+    <col min="5" max="5" width="3.22727272727273" customWidth="1"/>
+    <col min="6" max="6" width="8.87272727272727" customWidth="1"/>
+    <col min="7" max="7" width="10.8727272727273" customWidth="1"/>
     <col min="8" max="8" width="2.8" customWidth="1"/>
-    <col min="9" max="9" width="3.05" customWidth="1"/>
+    <col min="9" max="9" width="3.04545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3355,10 +3352,10 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>90</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3374,7 +3371,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7"/>
-      <c r="B5" s="11"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="2" t="s">
         <v>93</v>
       </c>
@@ -3385,40 +3382,40 @@
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="12" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="7"/>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>95</v>
       </c>
       <c r="E7" s="7"/>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="12" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="7"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="14" t="s">
         <v>96</v>
       </c>
       <c r="E8" s="7"/>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="12" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3427,34 +3424,34 @@
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="12" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="7"/>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>100</v>
       </c>
       <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="7"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="15" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="14" t="s">
         <v>101</v>
       </c>
       <c r="E11" s="7"/>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="17" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3463,35 +3460,35 @@
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="7"/>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="14" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="7"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="15" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="14" t="s">
         <v>106</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="19" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3500,95 +3497,95 @@
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="19" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="7"/>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="27"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="26"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="7"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="15" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="14" t="s">
         <v>111</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="27"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="26"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="27"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="26"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="26"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="26"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="27"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="26"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="26"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="27"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="26"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="26"/>
-      <c r="I23" s="28"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
+      <c r="I23" s="27"/>
     </row>
     <row r="24" spans="9:9">
-      <c r="I24" s="28"/>
+      <c r="I24" s="27"/>
     </row>
     <row r="25" spans="9:9">
-      <c r="I25" s="28"/>
+      <c r="I25" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="10">
